--- a/data/nzd0003/nzd0003.xlsx
+++ b/data/nzd0003/nzd0003.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH193"/>
+  <dimension ref="A1:AH194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21233,6 +21233,114 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>304.67</v>
+      </c>
+      <c r="C194" t="n">
+        <v>297.99</v>
+      </c>
+      <c r="D194" t="n">
+        <v>293.31</v>
+      </c>
+      <c r="E194" t="n">
+        <v>304.17</v>
+      </c>
+      <c r="F194" t="n">
+        <v>305.89</v>
+      </c>
+      <c r="G194" t="n">
+        <v>310.94</v>
+      </c>
+      <c r="H194" t="n">
+        <v>323.71</v>
+      </c>
+      <c r="I194" t="n">
+        <v>334.44</v>
+      </c>
+      <c r="J194" t="n">
+        <v>343.95</v>
+      </c>
+      <c r="K194" t="n">
+        <v>338.04</v>
+      </c>
+      <c r="L194" t="n">
+        <v>333.94</v>
+      </c>
+      <c r="M194" t="n">
+        <v>334.51</v>
+      </c>
+      <c r="N194" t="n">
+        <v>330.9</v>
+      </c>
+      <c r="O194" t="n">
+        <v>341.46</v>
+      </c>
+      <c r="P194" t="n">
+        <v>342.54</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>345.03</v>
+      </c>
+      <c r="R194" t="n">
+        <v>339.03</v>
+      </c>
+      <c r="S194" t="n">
+        <v>332.2</v>
+      </c>
+      <c r="T194" t="n">
+        <v>335.12</v>
+      </c>
+      <c r="U194" t="n">
+        <v>332.88</v>
+      </c>
+      <c r="V194" t="n">
+        <v>338.25</v>
+      </c>
+      <c r="W194" t="n">
+        <v>341.79</v>
+      </c>
+      <c r="X194" t="n">
+        <v>352.22</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>343.29</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>339.18</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>325.11</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>326.59</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>323.16</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>322.92</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>321.33</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>320.47</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>313.18</v>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21244,7 +21352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B194"/>
+  <dimension ref="A1:B195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23187,6 +23295,16 @@
       </c>
       <c r="B194" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>-0.91</v>
       </c>
     </row>
   </sheetData>
@@ -23355,28 +23473,28 @@
         <v>0.0366</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9453921300461924</v>
+        <v>0.918064107017197</v>
       </c>
       <c r="J2" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K2" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2001231238539575</v>
+        <v>0.1895472288564941</v>
       </c>
       <c r="M2" t="n">
-        <v>12.60508866449761</v>
+        <v>12.68943265607879</v>
       </c>
       <c r="N2" t="n">
-        <v>237.5296754781037</v>
+        <v>240.8952047977938</v>
       </c>
       <c r="O2" t="n">
-        <v>15.41199777699516</v>
+        <v>15.52079910306792</v>
       </c>
       <c r="P2" t="n">
-        <v>308.86344343751</v>
+        <v>309.125759262611</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23433,28 +23551,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9226065779920558</v>
+        <v>0.8931511688075996</v>
       </c>
       <c r="J3" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K3" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1894947594602907</v>
+        <v>0.178090630789871</v>
       </c>
       <c r="M3" t="n">
-        <v>12.40180225629366</v>
+        <v>12.4946825191435</v>
       </c>
       <c r="N3" t="n">
-        <v>244.5568132593989</v>
+        <v>248.6317916236717</v>
       </c>
       <c r="O3" t="n">
-        <v>15.63831235330075</v>
+        <v>15.76806239281389</v>
       </c>
       <c r="P3" t="n">
-        <v>305.028734733303</v>
+        <v>305.3085090959844</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23511,28 +23629,28 @@
         <v>0.0287</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3118129769765795</v>
+        <v>0.2818963857057006</v>
       </c>
       <c r="J4" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K4" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02200100734637622</v>
+        <v>0.01790620897467921</v>
       </c>
       <c r="M4" t="n">
-        <v>13.51485337804822</v>
+        <v>13.62532546925202</v>
       </c>
       <c r="N4" t="n">
-        <v>284.5665093309357</v>
+        <v>288.5353849175997</v>
       </c>
       <c r="O4" t="n">
-        <v>16.8690992448007</v>
+        <v>16.98632935385393</v>
       </c>
       <c r="P4" t="n">
-        <v>317.3476122523841</v>
+        <v>317.6353489701031</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23589,28 +23707,28 @@
         <v>0.035</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8114996444713508</v>
+        <v>0.785859615831967</v>
       </c>
       <c r="J5" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K5" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1577871712590679</v>
+        <v>0.1487064874286553</v>
       </c>
       <c r="M5" t="n">
-        <v>12.61887903022486</v>
+        <v>12.68304747680344</v>
       </c>
       <c r="N5" t="n">
-        <v>234.3579192220429</v>
+        <v>237.0592975701127</v>
       </c>
       <c r="O5" t="n">
-        <v>15.30875302635858</v>
+        <v>15.39673009343584</v>
       </c>
       <c r="P5" t="n">
-        <v>309.7077001201603</v>
+        <v>309.9506063953593</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23667,28 +23785,28 @@
         <v>0.0321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6021458973793785</v>
+        <v>0.5760713907882332</v>
       </c>
       <c r="J6" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K6" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09950176975879077</v>
+        <v>0.09114451272613755</v>
       </c>
       <c r="M6" t="n">
-        <v>11.8584352645372</v>
+        <v>11.929288882549</v>
       </c>
       <c r="N6" t="n">
-        <v>218.6459970458854</v>
+        <v>221.7142736298279</v>
       </c>
       <c r="O6" t="n">
-        <v>14.78668309817606</v>
+        <v>14.89007298940565</v>
       </c>
       <c r="P6" t="n">
-        <v>318.292051425147</v>
+        <v>318.539390477319</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23745,28 +23863,28 @@
         <v>0.034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3746265974057084</v>
+        <v>0.3518732698946363</v>
       </c>
       <c r="J7" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K7" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04536311832073647</v>
+        <v>0.04002321215408677</v>
       </c>
       <c r="M7" t="n">
-        <v>11.10114100415648</v>
+        <v>11.15063999072376</v>
       </c>
       <c r="N7" t="n">
-        <v>196.7970267002044</v>
+        <v>198.9747998875303</v>
       </c>
       <c r="O7" t="n">
-        <v>14.02843635977312</v>
+        <v>14.10584275708227</v>
       </c>
       <c r="P7" t="n">
-        <v>325.8179207541988</v>
+        <v>326.0337555751062</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23823,28 +23941,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4276357100778043</v>
+        <v>0.4114226298145092</v>
       </c>
       <c r="J8" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K8" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08325697432446455</v>
+        <v>0.07744543542831805</v>
       </c>
       <c r="M8" t="n">
-        <v>8.958651316627293</v>
+        <v>9.002579919205136</v>
       </c>
       <c r="N8" t="n">
-        <v>134.1717017044406</v>
+        <v>135.0981244382253</v>
       </c>
       <c r="O8" t="n">
-        <v>11.58325091260828</v>
+        <v>11.62317187510472</v>
       </c>
       <c r="P8" t="n">
-        <v>329.9925752277028</v>
+        <v>330.146370195638</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23901,28 +24019,28 @@
         <v>0.0436</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4345571083207784</v>
+        <v>0.4217366774202416</v>
       </c>
       <c r="J9" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K9" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1018647253654497</v>
+        <v>0.09665122744282029</v>
       </c>
       <c r="M9" t="n">
-        <v>8.10017433953313</v>
+        <v>8.125099554795467</v>
       </c>
       <c r="N9" t="n">
-        <v>110.9424266034457</v>
+        <v>111.3800891864771</v>
       </c>
       <c r="O9" t="n">
-        <v>10.53292108597827</v>
+        <v>10.55367657200452</v>
       </c>
       <c r="P9" t="n">
-        <v>336.8115402296439</v>
+        <v>336.9331530094022</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23979,28 +24097,28 @@
         <v>0.0433</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5392505272774357</v>
+        <v>0.5276407370463347</v>
       </c>
       <c r="J10" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K10" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1214856660928465</v>
+        <v>0.1174103298986573</v>
       </c>
       <c r="M10" t="n">
-        <v>8.766792703171223</v>
+        <v>8.784290752465958</v>
       </c>
       <c r="N10" t="n">
-        <v>140.117047827963</v>
+        <v>140.2186883846764</v>
       </c>
       <c r="O10" t="n">
-        <v>11.83710470630226</v>
+        <v>11.84139723109889</v>
       </c>
       <c r="P10" t="n">
-        <v>342.1779757513737</v>
+        <v>342.2881045663386</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24057,28 +24175,28 @@
         <v>0.0418</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5836274938460824</v>
+        <v>0.5700728794064295</v>
       </c>
       <c r="J11" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K11" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1433442275612899</v>
+        <v>0.1379486969813734</v>
       </c>
       <c r="M11" t="n">
-        <v>9.209965100035465</v>
+        <v>9.25919016131459</v>
       </c>
       <c r="N11" t="n">
-        <v>135.6387039202519</v>
+        <v>136.0670605260243</v>
       </c>
       <c r="O11" t="n">
-        <v>11.64640304644536</v>
+        <v>11.66477863167683</v>
       </c>
       <c r="P11" t="n">
-        <v>337.2086259857726</v>
+        <v>337.337203125913</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -24135,28 +24253,28 @@
         <v>0.0421</v>
       </c>
       <c r="I12" t="n">
-        <v>0.594822844764239</v>
+        <v>0.5814480971228424</v>
       </c>
       <c r="J12" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K12" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1418158888931912</v>
+        <v>0.1367205874297786</v>
       </c>
       <c r="M12" t="n">
-        <v>9.433160178012921</v>
+        <v>9.474156175168842</v>
       </c>
       <c r="N12" t="n">
-        <v>142.6648113245926</v>
+        <v>143.0263670244561</v>
       </c>
       <c r="O12" t="n">
-        <v>11.94423757820451</v>
+        <v>11.95936315296329</v>
       </c>
       <c r="P12" t="n">
-        <v>332.6059699426465</v>
+        <v>332.7328408919815</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -24213,28 +24331,28 @@
         <v>0.0429</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6607575672400551</v>
+        <v>0.6517964689340392</v>
       </c>
       <c r="J13" t="n">
+        <v>193</v>
+      </c>
+      <c r="K13" t="n">
         <v>192</v>
       </c>
-      <c r="K13" t="n">
-        <v>191</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.2221168186942341</v>
+        <v>0.21842649729105</v>
       </c>
       <c r="M13" t="n">
-        <v>8.055512349961834</v>
+        <v>8.070495000745138</v>
       </c>
       <c r="N13" t="n">
-        <v>102.8021957467333</v>
+        <v>102.7699579479596</v>
       </c>
       <c r="O13" t="n">
-        <v>10.13914176578735</v>
+        <v>10.13755187152991</v>
       </c>
       <c r="P13" t="n">
-        <v>326.6485774533174</v>
+        <v>326.732796229693</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24291,28 +24409,28 @@
         <v>0.0448</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5987813991650052</v>
+        <v>0.5882838389293097</v>
       </c>
       <c r="J14" t="n">
+        <v>193</v>
+      </c>
+      <c r="K14" t="n">
         <v>192</v>
       </c>
-      <c r="K14" t="n">
-        <v>191</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.197949038596771</v>
+        <v>0.1929604315742471</v>
       </c>
       <c r="M14" t="n">
-        <v>7.85515432769804</v>
+        <v>7.879589075759244</v>
       </c>
       <c r="N14" t="n">
-        <v>97.67205631254625</v>
+        <v>97.85388401448859</v>
       </c>
       <c r="O14" t="n">
-        <v>9.882917398852742</v>
+        <v>9.892112211984283</v>
       </c>
       <c r="P14" t="n">
-        <v>326.397182408725</v>
+        <v>326.4958412614445</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24369,28 +24487,28 @@
         <v>0.0419</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6792832508329335</v>
+        <v>0.6777916549733682</v>
       </c>
       <c r="J15" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K15" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2241545213830665</v>
+        <v>0.2252308611776355</v>
       </c>
       <c r="M15" t="n">
-        <v>8.093449173073155</v>
+        <v>8.061293616883772</v>
       </c>
       <c r="N15" t="n">
-        <v>107.4817293273121</v>
+        <v>106.932984876225</v>
       </c>
       <c r="O15" t="n">
-        <v>10.36733954914722</v>
+        <v>10.34084062715527</v>
       </c>
       <c r="P15" t="n">
-        <v>324.8371345903425</v>
+        <v>324.8511746639719</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24447,28 +24565,28 @@
         <v>0.0442</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7286079245937408</v>
+        <v>0.7286914226181876</v>
       </c>
       <c r="J16" t="n">
+        <v>193</v>
+      </c>
+      <c r="K16" t="n">
         <v>192</v>
       </c>
-      <c r="K16" t="n">
-        <v>191</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.2380136495534394</v>
+        <v>0.2400018215001261</v>
       </c>
       <c r="M16" t="n">
-        <v>8.643365646853431</v>
+        <v>8.598662329627977</v>
       </c>
       <c r="N16" t="n">
-        <v>113.7794188871887</v>
+        <v>113.1868613645837</v>
       </c>
       <c r="O16" t="n">
-        <v>10.66674359339291</v>
+        <v>10.63893140144177</v>
       </c>
       <c r="P16" t="n">
-        <v>322.8463606747754</v>
+        <v>322.8455721411539</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24525,28 +24643,28 @@
         <v>0.0482</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6821095856217865</v>
+        <v>0.6843961917891528</v>
       </c>
       <c r="J17" t="n">
+        <v>193</v>
+      </c>
+      <c r="K17" t="n">
         <v>192</v>
       </c>
-      <c r="K17" t="n">
-        <v>191</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.231917700399687</v>
+        <v>0.2349735561929818</v>
       </c>
       <c r="M17" t="n">
-        <v>8.253526003170824</v>
+        <v>8.219598234105627</v>
       </c>
       <c r="N17" t="n">
-        <v>103.1603408371129</v>
+        <v>102.6557581404438</v>
       </c>
       <c r="O17" t="n">
-        <v>10.15678791927413</v>
+        <v>10.1319177918321</v>
       </c>
       <c r="P17" t="n">
-        <v>324.1588498147443</v>
+        <v>324.1372557009422</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24603,28 +24721,28 @@
         <v>0.0524</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6369006329374454</v>
+        <v>0.6371495565066885</v>
       </c>
       <c r="J18" t="n">
+        <v>193</v>
+      </c>
+      <c r="K18" t="n">
         <v>192</v>
       </c>
-      <c r="K18" t="n">
-        <v>191</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.158444218848343</v>
+        <v>0.1599811163789536</v>
       </c>
       <c r="M18" t="n">
-        <v>10.3851211180094</v>
+        <v>10.3320588192028</v>
       </c>
       <c r="N18" t="n">
-        <v>144.2382594903624</v>
+        <v>143.4874062054701</v>
       </c>
       <c r="O18" t="n">
-        <v>12.00992337570737</v>
+        <v>11.97862288434986</v>
       </c>
       <c r="P18" t="n">
-        <v>321.621178447848</v>
+        <v>321.6188276784156</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24681,28 +24799,28 @@
         <v>0.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4764975187385918</v>
+        <v>0.4754678191312695</v>
       </c>
       <c r="J19" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K19" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1116502478232393</v>
+        <v>0.1122811556833236</v>
       </c>
       <c r="M19" t="n">
-        <v>9.12886362968589</v>
+        <v>9.088222673711966</v>
       </c>
       <c r="N19" t="n">
-        <v>120.8284514514251</v>
+        <v>120.2090094109826</v>
       </c>
       <c r="O19" t="n">
-        <v>10.99219957294376</v>
+        <v>10.96398693044563</v>
       </c>
       <c r="P19" t="n">
-        <v>320.524173142903</v>
+        <v>320.5338822101917</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24759,28 +24877,28 @@
         <v>0.0506</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3649607952295507</v>
+        <v>0.3679621187153239</v>
       </c>
       <c r="J20" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K20" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L20" t="n">
-        <v>0.06920229535832523</v>
+        <v>0.07093781532141186</v>
       </c>
       <c r="M20" t="n">
-        <v>9.053424015257912</v>
+        <v>9.021101080025776</v>
       </c>
       <c r="N20" t="n">
-        <v>119.8259444837028</v>
+        <v>119.2612598810865</v>
       </c>
       <c r="O20" t="n">
-        <v>10.94650375616355</v>
+        <v>10.92068037629005</v>
       </c>
       <c r="P20" t="n">
-        <v>321.9897699871551</v>
+        <v>321.9614704214648</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24837,28 +24955,28 @@
         <v>0.0544</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5173890838521754</v>
+        <v>0.5163028143095001</v>
       </c>
       <c r="J21" t="n">
+        <v>193</v>
+      </c>
+      <c r="K21" t="n">
         <v>192</v>
       </c>
-      <c r="K21" t="n">
-        <v>191</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.1330426855400758</v>
+        <v>0.1337867019518452</v>
       </c>
       <c r="M21" t="n">
-        <v>8.794710517191293</v>
+        <v>8.756174981254807</v>
       </c>
       <c r="N21" t="n">
-        <v>116.7809052505071</v>
+        <v>116.1800535196225</v>
       </c>
       <c r="O21" t="n">
-        <v>10.80652142229437</v>
+        <v>10.77868514799567</v>
       </c>
       <c r="P21" t="n">
-        <v>320.1690206367745</v>
+        <v>320.1792790837511</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24915,28 +25033,28 @@
         <v>0.0505</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3827653060497535</v>
+        <v>0.3861608806325477</v>
       </c>
       <c r="J22" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K22" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05979331100083873</v>
+        <v>0.06138246558716942</v>
       </c>
       <c r="M22" t="n">
-        <v>10.18362222420589</v>
+        <v>10.14403084242388</v>
       </c>
       <c r="N22" t="n">
-        <v>154.0846921276282</v>
+        <v>153.3582286244308</v>
       </c>
       <c r="O22" t="n">
-        <v>12.41308552003201</v>
+        <v>12.38378894460136</v>
       </c>
       <c r="P22" t="n">
-        <v>324.1982397647619</v>
+        <v>324.1662227941096</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -24993,28 +25111,28 @@
         <v>0.0567</v>
       </c>
       <c r="I23" t="n">
-        <v>0.383903373981538</v>
+        <v>0.3885130741559381</v>
       </c>
       <c r="J23" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K23" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06126355661881899</v>
+        <v>0.06323157643966537</v>
       </c>
       <c r="M23" t="n">
-        <v>9.796718253147935</v>
+        <v>9.770006061703857</v>
       </c>
       <c r="N23" t="n">
-        <v>151.0459060963797</v>
+        <v>150.3957996485543</v>
       </c>
       <c r="O23" t="n">
-        <v>12.29007347807082</v>
+        <v>12.26359652176124</v>
       </c>
       <c r="P23" t="n">
-        <v>326.3683240947053</v>
+        <v>326.3248590988405</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -25071,28 +25189,28 @@
         <v>0.0536</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4821490356054249</v>
+        <v>0.4917135493605916</v>
       </c>
       <c r="J24" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K24" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1014033500754219</v>
+        <v>0.1056591664039862</v>
       </c>
       <c r="M24" t="n">
-        <v>9.399360657131529</v>
+        <v>9.400336153506387</v>
       </c>
       <c r="N24" t="n">
-        <v>137.7839799508516</v>
+        <v>137.6405592117263</v>
       </c>
       <c r="O24" t="n">
-        <v>11.73814209961916</v>
+        <v>11.73203133356395</v>
       </c>
       <c r="P24" t="n">
-        <v>328.6749061664032</v>
+        <v>328.5847220904135</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -25149,28 +25267,28 @@
         <v>0.0562</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2658172761556443</v>
+        <v>0.2702977545698088</v>
       </c>
       <c r="J25" t="n">
+        <v>193</v>
+      </c>
+      <c r="K25" t="n">
         <v>192</v>
       </c>
-      <c r="K25" t="n">
-        <v>191</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.02912714792825877</v>
+        <v>0.03037784462252058</v>
       </c>
       <c r="M25" t="n">
-        <v>10.25540703266981</v>
+        <v>10.22716706012126</v>
       </c>
       <c r="N25" t="n">
-        <v>157.6744791060541</v>
+        <v>156.9788482699592</v>
       </c>
       <c r="O25" t="n">
-        <v>12.55684988785221</v>
+        <v>12.52912001179489</v>
       </c>
       <c r="P25" t="n">
-        <v>331.1926169816361</v>
+        <v>331.1503045090537</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -25227,28 +25345,28 @@
         <v>0.064</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2513160742930027</v>
+        <v>0.2556234690388269</v>
       </c>
       <c r="J26" t="n">
+        <v>193</v>
+      </c>
+      <c r="K26" t="n">
         <v>192</v>
       </c>
-      <c r="K26" t="n">
-        <v>191</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.02156078869992784</v>
+        <v>0.02251226989572452</v>
       </c>
       <c r="M26" t="n">
-        <v>11.20575885563618</v>
+        <v>11.16509524988806</v>
       </c>
       <c r="N26" t="n">
-        <v>192.5051460833948</v>
+        <v>191.618207278409</v>
       </c>
       <c r="O26" t="n">
-        <v>13.87462237624487</v>
+        <v>13.84262284678771</v>
       </c>
       <c r="P26" t="n">
-        <v>327.6655415165953</v>
+        <v>327.625071820676</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -25305,28 +25423,28 @@
         <v>0.0554</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3666217329815805</v>
+        <v>0.361418435550555</v>
       </c>
       <c r="J27" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K27" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L27" t="n">
-        <v>0.03777703572422342</v>
+        <v>0.03710662263429176</v>
       </c>
       <c r="M27" t="n">
-        <v>11.95491871832004</v>
+        <v>11.93473776027656</v>
       </c>
       <c r="N27" t="n">
-        <v>228.985446497623</v>
+        <v>227.9678338257908</v>
       </c>
       <c r="O27" t="n">
-        <v>15.13226508152772</v>
+        <v>15.09860370450827</v>
       </c>
       <c r="P27" t="n">
-        <v>321.0064962416126</v>
+        <v>321.0555582831265</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -25383,28 +25501,28 @@
         <v>0.0452</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2486019201641688</v>
+        <v>0.2457136141263087</v>
       </c>
       <c r="J28" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K28" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02243288492777207</v>
+        <v>0.02215095369794928</v>
       </c>
       <c r="M28" t="n">
-        <v>10.88430794953198</v>
+        <v>10.84455329004882</v>
       </c>
       <c r="N28" t="n">
-        <v>180.1333148354359</v>
+        <v>179.2520058126731</v>
       </c>
       <c r="O28" t="n">
-        <v>13.42137529597604</v>
+        <v>13.38850274723328</v>
       </c>
       <c r="P28" t="n">
-        <v>323.1008039506626</v>
+        <v>323.1280378715778</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -25461,28 +25579,28 @@
         <v>0.0527</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1956800117898385</v>
+        <v>0.1914136640896963</v>
       </c>
       <c r="J29" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K29" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01700455861590533</v>
+        <v>0.01644334802406033</v>
       </c>
       <c r="M29" t="n">
-        <v>10.25709990481732</v>
+        <v>10.22792214303767</v>
       </c>
       <c r="N29" t="n">
-        <v>148.0480530577621</v>
+        <v>147.3944740432058</v>
       </c>
       <c r="O29" t="n">
-        <v>12.16749986882112</v>
+        <v>12.14061258928914</v>
       </c>
       <c r="P29" t="n">
-        <v>322.614797570251</v>
+        <v>322.6550250857354</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -25539,28 +25657,28 @@
         <v>0.0524</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2471080899664289</v>
+        <v>0.2424217032732456</v>
       </c>
       <c r="J30" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K30" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02524474966020129</v>
+        <v>0.02455428660862835</v>
       </c>
       <c r="M30" t="n">
-        <v>10.22366721621351</v>
+        <v>10.19788839006026</v>
       </c>
       <c r="N30" t="n">
-        <v>157.6965059419894</v>
+        <v>157.0163861087826</v>
       </c>
       <c r="O30" t="n">
-        <v>12.55772694168771</v>
+        <v>12.5306179460066</v>
       </c>
       <c r="P30" t="n">
-        <v>321.4527208480334</v>
+        <v>321.4969089232951</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -25617,28 +25735,28 @@
         <v>0.0501</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3454871740637722</v>
+        <v>0.3389885763806103</v>
       </c>
       <c r="J31" t="n">
+        <v>193</v>
+      </c>
+      <c r="K31" t="n">
         <v>192</v>
       </c>
-      <c r="K31" t="n">
-        <v>191</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.05565636814069475</v>
+        <v>0.05413973323732824</v>
       </c>
       <c r="M31" t="n">
-        <v>9.115912147537452</v>
+        <v>9.108847781058934</v>
       </c>
       <c r="N31" t="n">
-        <v>135.5843781240074</v>
+        <v>135.1424181183098</v>
       </c>
       <c r="O31" t="n">
-        <v>11.64407051352779</v>
+        <v>11.62507712311234</v>
       </c>
       <c r="P31" t="n">
-        <v>319.2135190374596</v>
+        <v>319.2748901034209</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -25695,28 +25813,28 @@
         <v>0.0491</v>
       </c>
       <c r="I32" t="n">
-        <v>0.301307317917718</v>
+        <v>0.29735968675642</v>
       </c>
       <c r="J32" t="n">
+        <v>193</v>
+      </c>
+      <c r="K32" t="n">
         <v>192</v>
       </c>
-      <c r="K32" t="n">
-        <v>191</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.05662817678878251</v>
+        <v>0.05574568532405699</v>
       </c>
       <c r="M32" t="n">
-        <v>7.955483527961834</v>
+        <v>7.938529422024897</v>
       </c>
       <c r="N32" t="n">
-        <v>101.2512241564539</v>
+        <v>100.8213686917307</v>
       </c>
       <c r="O32" t="n">
-        <v>10.06236672738844</v>
+        <v>10.04098444833626</v>
       </c>
       <c r="P32" t="n">
-        <v>316.7286393890259</v>
+        <v>316.7659197907683</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -25773,28 +25891,28 @@
         <v>0.0427</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2422825193236586</v>
+        <v>0.2345230820122387</v>
       </c>
       <c r="J33" t="n">
+        <v>193</v>
+      </c>
+      <c r="K33" t="n">
         <v>192</v>
       </c>
-      <c r="K33" t="n">
-        <v>191</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.03209261697391919</v>
+        <v>0.03035117715462821</v>
       </c>
       <c r="M33" t="n">
-        <v>8.527816058457889</v>
+        <v>8.522041902618939</v>
       </c>
       <c r="N33" t="n">
-        <v>118.5232178282049</v>
+        <v>118.2825855795232</v>
       </c>
       <c r="O33" t="n">
-        <v>10.88683690647586</v>
+        <v>10.87577976880385</v>
       </c>
       <c r="P33" t="n">
-        <v>315.2356187592841</v>
+        <v>315.3088968666972</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -25832,7 +25950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH193"/>
+  <dimension ref="A1:AH194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58819,6 +58937,178 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>-34.4229761421546,173.01239071531523</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>-34.42360434432844,173.0119089119381</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>-34.424240910182,173.01144638880714</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-34.424942499185434,173.01113367973926</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-34.425605836167314,173.01073285653376</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-34.42628310285652,173.0103641371301</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-34.4269926699594,173.0100698452633</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-34.42769369565044,173.00975588776762</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>-34.42840186326147,173.00942263792263</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>-34.42909765139438,173.00905788960256</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>-34.429793222863886,173.0087361044833</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>-34.43049930549066,173.00846370787147</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>-34.431193722369485,173.00814804752167</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>-34.4319276596414,173.00797905007232</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>-34.43263666125006,173.007711310983</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>-34.43335802827858,173.00746998497974</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>-34.43407191890486,173.00719654196257</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>-34.43477843842637,173.00691616041658</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>-34.43550528275935,173.0067390254943</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>-34.436221360989926,173.00650724871224</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>-34.43695330187629,173.00635605911805</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>-34.43768142058597,173.00618549117027</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>-34.4384271520361,173.00608692295222</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>-34.43915035621329,173.00583312377248</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>-34.43988752269746,173.00568334338593</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>-34.44060863830288,173.00542682704247</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>-34.44134601577072,173.0053384307304</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>-34.442078249843874,173.00519694856334</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>-34.44281381485167,173.00508995582067</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>-34.443555302609006,173.004967386893</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>-34.44430284572347,173.0048863178117</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>-34.44504009926808,173.00474718112474</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0003/nzd0003.xlsx
+++ b/data/nzd0003/nzd0003.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH194"/>
+  <dimension ref="A1:AH195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21306,13 +21306,13 @@
         <v>341.79</v>
       </c>
       <c r="X194" t="n">
-        <v>352.22</v>
+        <v>346.17</v>
       </c>
       <c r="Y194" t="n">
-        <v>343.29</v>
+        <v>338.81</v>
       </c>
       <c r="Z194" t="n">
-        <v>339.18</v>
+        <v>333.4</v>
       </c>
       <c r="AA194" t="n">
         <v>325.11</v>
@@ -21338,6 +21338,114 @@
       <c r="AH194" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>303.75</v>
+      </c>
+      <c r="C195" t="n">
+        <v>298.4</v>
+      </c>
+      <c r="D195" t="n">
+        <v>294.21</v>
+      </c>
+      <c r="E195" t="n">
+        <v>305.51</v>
+      </c>
+      <c r="F195" t="n">
+        <v>306.8</v>
+      </c>
+      <c r="G195" t="n">
+        <v>310.7</v>
+      </c>
+      <c r="H195" t="n">
+        <v>323.48</v>
+      </c>
+      <c r="I195" t="n">
+        <v>334.65</v>
+      </c>
+      <c r="J195" t="n">
+        <v>343.64</v>
+      </c>
+      <c r="K195" t="n">
+        <v>337.94</v>
+      </c>
+      <c r="L195" t="n">
+        <v>334.72</v>
+      </c>
+      <c r="M195" t="n">
+        <v>334.71</v>
+      </c>
+      <c r="N195" t="n">
+        <v>331.82</v>
+      </c>
+      <c r="O195" t="n">
+        <v>340.88</v>
+      </c>
+      <c r="P195" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>345.17</v>
+      </c>
+      <c r="R195" t="n">
+        <v>337.75</v>
+      </c>
+      <c r="S195" t="n">
+        <v>332.68</v>
+      </c>
+      <c r="T195" t="n">
+        <v>333.58</v>
+      </c>
+      <c r="U195" t="n">
+        <v>331.65</v>
+      </c>
+      <c r="V195" t="n">
+        <v>335.71</v>
+      </c>
+      <c r="W195" t="n">
+        <v>339.04</v>
+      </c>
+      <c r="X195" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>338.22</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>332.38</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>325.23</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>325.57</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>323.04</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>323.16</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>321.18</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>320.08</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>312.13</v>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21352,7 +21460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B195"/>
+  <dimension ref="A1:B196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23305,6 +23413,16 @@
       </c>
       <c r="B195" t="n">
         <v>-0.91</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -23473,28 +23591,28 @@
         <v>0.0366</v>
       </c>
       <c r="I2" t="n">
-        <v>0.918064107017197</v>
+        <v>0.8904120519883304</v>
       </c>
       <c r="J2" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K2" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1895472288564941</v>
+        <v>0.178984012500701</v>
       </c>
       <c r="M2" t="n">
-        <v>12.68943265607879</v>
+        <v>12.77619305603893</v>
       </c>
       <c r="N2" t="n">
-        <v>240.8952047977938</v>
+        <v>244.3972995905273</v>
       </c>
       <c r="O2" t="n">
-        <v>15.52079910306792</v>
+        <v>15.63321142921464</v>
       </c>
       <c r="P2" t="n">
-        <v>309.125759262611</v>
+        <v>309.3927095024916</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23551,28 +23669,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8931511688075996</v>
+        <v>0.8646542194973921</v>
       </c>
       <c r="J3" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L3" t="n">
-        <v>0.178090630789871</v>
+        <v>0.1674505234105542</v>
       </c>
       <c r="M3" t="n">
-        <v>12.4946825191435</v>
+        <v>12.58355941885072</v>
       </c>
       <c r="N3" t="n">
-        <v>248.6317916236717</v>
+        <v>252.3876321022052</v>
       </c>
       <c r="O3" t="n">
-        <v>15.76806239281389</v>
+        <v>15.8867124384564</v>
       </c>
       <c r="P3" t="n">
-        <v>305.3085090959844</v>
+        <v>305.5807441309896</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23629,28 +23747,28 @@
         <v>0.0287</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2818963857057006</v>
+        <v>0.2534516677891331</v>
       </c>
       <c r="J4" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K4" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01790620897467921</v>
+        <v>0.01443207804687774</v>
       </c>
       <c r="M4" t="n">
-        <v>13.62532546925202</v>
+        <v>13.72535382387976</v>
       </c>
       <c r="N4" t="n">
-        <v>288.5353849175997</v>
+        <v>292.0052375119104</v>
       </c>
       <c r="O4" t="n">
-        <v>16.98632935385393</v>
+        <v>17.08816074104848</v>
       </c>
       <c r="P4" t="n">
-        <v>317.6353489701031</v>
+        <v>317.9104622508017</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23707,28 +23825,28 @@
         <v>0.035</v>
       </c>
       <c r="I5" t="n">
-        <v>0.785859615831967</v>
+        <v>0.7619837736704199</v>
       </c>
       <c r="J5" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K5" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1487064874286553</v>
+        <v>0.1406324631376976</v>
       </c>
       <c r="M5" t="n">
-        <v>12.68304747680344</v>
+        <v>12.73766975919884</v>
       </c>
       <c r="N5" t="n">
-        <v>237.0592975701127</v>
+        <v>239.2570573180076</v>
       </c>
       <c r="O5" t="n">
-        <v>15.39673009343584</v>
+        <v>15.4679364272681</v>
       </c>
       <c r="P5" t="n">
-        <v>309.9506063953593</v>
+        <v>310.1780716093829</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23785,28 +23903,28 @@
         <v>0.0321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5760713907882332</v>
+        <v>0.5513433056401299</v>
       </c>
       <c r="J6" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K6" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09114451272613755</v>
+        <v>0.08363666663178038</v>
       </c>
       <c r="M6" t="n">
-        <v>11.929288882549</v>
+        <v>12.00814420498012</v>
       </c>
       <c r="N6" t="n">
-        <v>221.7142736298279</v>
+        <v>224.3792851215685</v>
       </c>
       <c r="O6" t="n">
-        <v>14.89007298940565</v>
+        <v>14.97929521444746</v>
       </c>
       <c r="P6" t="n">
-        <v>318.539390477319</v>
+        <v>318.775277661795</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23863,28 +23981,28 @@
         <v>0.034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3518732698946363</v>
+        <v>0.3293716497491357</v>
       </c>
       <c r="J7" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K7" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04002321215408677</v>
+        <v>0.03506883266726712</v>
       </c>
       <c r="M7" t="n">
-        <v>11.15063999072376</v>
+        <v>11.20251765943118</v>
       </c>
       <c r="N7" t="n">
-        <v>198.9747998875303</v>
+        <v>201.101363586748</v>
       </c>
       <c r="O7" t="n">
-        <v>14.10584275708227</v>
+        <v>14.18102124625543</v>
       </c>
       <c r="P7" t="n">
-        <v>326.0337555751062</v>
+        <v>326.2484039714733</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23941,28 +24059,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4114226298145092</v>
+        <v>0.3953155954200048</v>
       </c>
       <c r="J8" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K8" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07744543542831805</v>
+        <v>0.07184380010896119</v>
       </c>
       <c r="M8" t="n">
-        <v>9.002579919205136</v>
+        <v>9.045787669720324</v>
       </c>
       <c r="N8" t="n">
-        <v>135.0981244382253</v>
+        <v>136.0151329852702</v>
       </c>
       <c r="O8" t="n">
-        <v>11.62317187510472</v>
+        <v>11.66255259303341</v>
       </c>
       <c r="P8" t="n">
-        <v>330.146370195638</v>
+        <v>330.3000190920576</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24019,28 +24137,28 @@
         <v>0.0436</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4217366774202416</v>
+        <v>0.4093501398804406</v>
       </c>
       <c r="J9" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K9" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09665122744282029</v>
+        <v>0.0917455067109354</v>
       </c>
       <c r="M9" t="n">
-        <v>8.125099554795467</v>
+        <v>8.151150221221654</v>
       </c>
       <c r="N9" t="n">
-        <v>111.3800891864771</v>
+        <v>111.7584058707387</v>
       </c>
       <c r="O9" t="n">
-        <v>10.55367657200452</v>
+        <v>10.57158483249975</v>
       </c>
       <c r="P9" t="n">
-        <v>336.9331530094022</v>
+        <v>337.0513111865587</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24097,28 +24215,28 @@
         <v>0.0433</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5276407370463347</v>
+        <v>0.5159550911076539</v>
       </c>
       <c r="J10" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K10" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1174103298986573</v>
+        <v>0.1133121065349826</v>
       </c>
       <c r="M10" t="n">
-        <v>8.784290752465958</v>
+        <v>8.801427257577433</v>
       </c>
       <c r="N10" t="n">
-        <v>140.2186883846764</v>
+        <v>140.3414083155148</v>
       </c>
       <c r="O10" t="n">
-        <v>11.84139723109889</v>
+        <v>11.84657791581665</v>
       </c>
       <c r="P10" t="n">
-        <v>342.2881045663386</v>
+        <v>342.3995767690081</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24175,28 +24293,28 @@
         <v>0.0418</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5700728794064295</v>
+        <v>0.556671748880519</v>
       </c>
       <c r="J11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K11" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1379486969813734</v>
+        <v>0.1326720626927312</v>
       </c>
       <c r="M11" t="n">
-        <v>9.25919016131459</v>
+        <v>9.307312458310703</v>
       </c>
       <c r="N11" t="n">
-        <v>136.0670605260243</v>
+        <v>136.4802400591187</v>
       </c>
       <c r="O11" t="n">
-        <v>11.66477863167683</v>
+        <v>11.68247576753826</v>
       </c>
       <c r="P11" t="n">
-        <v>337.337203125913</v>
+        <v>337.4650397509335</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -24253,28 +24371,28 @@
         <v>0.0421</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5814480971228424</v>
+        <v>0.5690204519096984</v>
       </c>
       <c r="J12" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K12" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1367205874297786</v>
+        <v>0.1321546499799408</v>
       </c>
       <c r="M12" t="n">
-        <v>9.474156175168842</v>
+        <v>9.508901537156214</v>
       </c>
       <c r="N12" t="n">
-        <v>143.0263670244561</v>
+        <v>143.2462313996117</v>
       </c>
       <c r="O12" t="n">
-        <v>11.95936315296329</v>
+        <v>11.96855176701057</v>
       </c>
       <c r="P12" t="n">
-        <v>332.7328408919815</v>
+        <v>332.8513912051757</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -24331,28 +24449,28 @@
         <v>0.0429</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6517964689340392</v>
+        <v>0.6431449460968826</v>
       </c>
       <c r="J13" t="n">
+        <v>194</v>
+      </c>
+      <c r="K13" t="n">
         <v>193</v>
       </c>
-      <c r="K13" t="n">
-        <v>192</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.21842649729105</v>
+        <v>0.2149242017315527</v>
       </c>
       <c r="M13" t="n">
-        <v>8.070495000745138</v>
+        <v>8.084006151458214</v>
       </c>
       <c r="N13" t="n">
-        <v>102.7699579479596</v>
+        <v>102.7103027369663</v>
       </c>
       <c r="O13" t="n">
-        <v>10.13755187152991</v>
+        <v>10.13460915560962</v>
       </c>
       <c r="P13" t="n">
-        <v>326.732796229693</v>
+        <v>326.8145659906052</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24409,28 +24527,28 @@
         <v>0.0448</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5882838389293097</v>
+        <v>0.578789710114394</v>
       </c>
       <c r="J14" t="n">
+        <v>194</v>
+      </c>
+      <c r="K14" t="n">
         <v>193</v>
       </c>
-      <c r="K14" t="n">
-        <v>192</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1929604315742471</v>
+        <v>0.1886881063255679</v>
       </c>
       <c r="M14" t="n">
-        <v>7.879589075759244</v>
+        <v>7.897314125417924</v>
       </c>
       <c r="N14" t="n">
-        <v>97.85388401448859</v>
+        <v>97.91628764929717</v>
       </c>
       <c r="O14" t="n">
-        <v>9.892112211984283</v>
+        <v>9.895265921100714</v>
       </c>
       <c r="P14" t="n">
-        <v>326.4958412614445</v>
+        <v>326.5855749023165</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24487,28 +24605,28 @@
         <v>0.0419</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6777916549733682</v>
+        <v>0.6757437761544334</v>
       </c>
       <c r="J15" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K15" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2252308611776355</v>
+        <v>0.2259955835514463</v>
       </c>
       <c r="M15" t="n">
-        <v>8.061293616883772</v>
+        <v>8.03314857302999</v>
       </c>
       <c r="N15" t="n">
-        <v>106.932984876225</v>
+        <v>106.4026194669635</v>
       </c>
       <c r="O15" t="n">
-        <v>10.34084062715527</v>
+        <v>10.31516453901553</v>
       </c>
       <c r="P15" t="n">
-        <v>324.8511746639719</v>
+        <v>324.8705607288048</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24565,28 +24683,28 @@
         <v>0.0442</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7286914226181876</v>
+        <v>0.7284657235989541</v>
       </c>
       <c r="J16" t="n">
+        <v>194</v>
+      </c>
+      <c r="K16" t="n">
         <v>193</v>
       </c>
-      <c r="K16" t="n">
-        <v>192</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.2400018215001261</v>
+        <v>0.241840374265477</v>
       </c>
       <c r="M16" t="n">
-        <v>8.598662329627977</v>
+        <v>8.555835850120038</v>
       </c>
       <c r="N16" t="n">
-        <v>113.1868613645837</v>
+        <v>112.6007221805698</v>
       </c>
       <c r="O16" t="n">
-        <v>10.63893140144177</v>
+        <v>10.61134874464928</v>
       </c>
       <c r="P16" t="n">
-        <v>322.8455721411539</v>
+        <v>322.8477156278052</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24643,28 +24761,28 @@
         <v>0.0482</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6843961917891528</v>
+        <v>0.6866858139211082</v>
       </c>
       <c r="J17" t="n">
+        <v>194</v>
+      </c>
+      <c r="K17" t="n">
         <v>193</v>
       </c>
-      <c r="K17" t="n">
-        <v>192</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.2349735561929818</v>
+        <v>0.2380490491032526</v>
       </c>
       <c r="M17" t="n">
-        <v>8.219598234105627</v>
+        <v>8.185916187023894</v>
       </c>
       <c r="N17" t="n">
-        <v>102.6557581404438</v>
+        <v>102.1569223932938</v>
       </c>
       <c r="O17" t="n">
-        <v>10.1319177918321</v>
+        <v>10.10727076877303</v>
       </c>
       <c r="P17" t="n">
-        <v>324.1372557009422</v>
+        <v>324.1155109255636</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24721,28 +24839,28 @@
         <v>0.0524</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6371495565066885</v>
+        <v>0.6361808422958549</v>
       </c>
       <c r="J18" t="n">
+        <v>194</v>
+      </c>
+      <c r="K18" t="n">
         <v>193</v>
       </c>
-      <c r="K18" t="n">
-        <v>192</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1599811163789536</v>
+        <v>0.1610039298518761</v>
       </c>
       <c r="M18" t="n">
-        <v>10.3320588192028</v>
+        <v>10.28558575763523</v>
       </c>
       <c r="N18" t="n">
-        <v>143.4874062054701</v>
+        <v>142.7498659155013</v>
       </c>
       <c r="O18" t="n">
-        <v>11.97862288434986</v>
+        <v>11.94779753408558</v>
       </c>
       <c r="P18" t="n">
-        <v>321.6188276784156</v>
+        <v>321.6280276562751</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24799,28 +24917,28 @@
         <v>0.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4754678191312695</v>
+        <v>0.4748439660283699</v>
       </c>
       <c r="J19" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K19" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1122811556833236</v>
+        <v>0.1130864185487086</v>
       </c>
       <c r="M19" t="n">
-        <v>9.088222673711966</v>
+        <v>9.045355975770827</v>
       </c>
       <c r="N19" t="n">
-        <v>120.2090094109826</v>
+        <v>119.5918220330661</v>
       </c>
       <c r="O19" t="n">
-        <v>10.96398693044563</v>
+        <v>10.93580459010978</v>
       </c>
       <c r="P19" t="n">
-        <v>320.5338822101917</v>
+        <v>320.5397975813111</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24877,28 +24995,28 @@
         <v>0.0506</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3679621187153239</v>
+        <v>0.3694712204523077</v>
       </c>
       <c r="J20" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K20" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07093781532141186</v>
+        <v>0.07218454726107626</v>
       </c>
       <c r="M20" t="n">
-        <v>9.021101080025776</v>
+        <v>8.98198861281988</v>
       </c>
       <c r="N20" t="n">
-        <v>119.2612598810865</v>
+        <v>118.6608281022018</v>
       </c>
       <c r="O20" t="n">
-        <v>10.92068037629005</v>
+        <v>10.89315510319218</v>
       </c>
       <c r="P20" t="n">
-        <v>321.9614704214648</v>
+        <v>321.9471611284762</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24955,28 +25073,28 @@
         <v>0.0544</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5163028143095001</v>
+        <v>0.5140779551030256</v>
       </c>
       <c r="J21" t="n">
+        <v>194</v>
+      </c>
+      <c r="K21" t="n">
         <v>193</v>
       </c>
-      <c r="K21" t="n">
-        <v>192</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.1337867019518452</v>
+        <v>0.1339918155664735</v>
       </c>
       <c r="M21" t="n">
-        <v>8.756174981254807</v>
+        <v>8.725500373579363</v>
       </c>
       <c r="N21" t="n">
-        <v>116.1800535196225</v>
+        <v>115.6092999562591</v>
       </c>
       <c r="O21" t="n">
-        <v>10.77868514799567</v>
+        <v>10.7521765218145</v>
       </c>
       <c r="P21" t="n">
-        <v>320.1792790837511</v>
+        <v>320.2004087990079</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -25033,28 +25151,28 @@
         <v>0.0505</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3861608806325477</v>
+        <v>0.3871600246319992</v>
       </c>
       <c r="J22" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K22" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L22" t="n">
-        <v>0.06138246558716942</v>
+        <v>0.06230069143363226</v>
       </c>
       <c r="M22" t="n">
-        <v>10.14403084242388</v>
+        <v>10.09555086659257</v>
       </c>
       <c r="N22" t="n">
-        <v>153.3582286244308</v>
+        <v>152.5739981138181</v>
       </c>
       <c r="O22" t="n">
-        <v>12.38378894460136</v>
+        <v>12.35208476791744</v>
       </c>
       <c r="P22" t="n">
-        <v>324.1662227941096</v>
+        <v>324.1567489171168</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -25111,28 +25229,28 @@
         <v>0.0567</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3885130741559381</v>
+        <v>0.3905061642381405</v>
       </c>
       <c r="J23" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K23" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06323157643966537</v>
+        <v>0.0644728954573196</v>
       </c>
       <c r="M23" t="n">
-        <v>9.770006061703857</v>
+        <v>9.729966188145738</v>
       </c>
       <c r="N23" t="n">
-        <v>150.3957996485543</v>
+        <v>149.6455364311553</v>
       </c>
       <c r="O23" t="n">
-        <v>12.26359652176124</v>
+        <v>12.23296924017858</v>
       </c>
       <c r="P23" t="n">
-        <v>326.3248590988405</v>
+        <v>326.3059606314677</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -25189,28 +25307,28 @@
         <v>0.0536</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4917135493605916</v>
+        <v>0.4881835197449665</v>
       </c>
       <c r="J24" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K24" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1056591664039862</v>
+        <v>0.1056127103130778</v>
       </c>
       <c r="M24" t="n">
-        <v>9.400336153506387</v>
+        <v>9.333482042933737</v>
       </c>
       <c r="N24" t="n">
-        <v>137.6405592117263</v>
+        <v>136.4911331764469</v>
       </c>
       <c r="O24" t="n">
-        <v>11.73203133356395</v>
+        <v>11.68294197436788</v>
       </c>
       <c r="P24" t="n">
-        <v>328.5847220904135</v>
+        <v>328.6179039632276</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -25267,28 +25385,28 @@
         <v>0.0562</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2702977545698088</v>
+        <v>0.2661018004457419</v>
       </c>
       <c r="J25" t="n">
+        <v>194</v>
+      </c>
+      <c r="K25" t="n">
         <v>193</v>
       </c>
-      <c r="K25" t="n">
-        <v>192</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.03037784462252058</v>
+        <v>0.0297993882047376</v>
       </c>
       <c r="M25" t="n">
-        <v>10.22716706012126</v>
+        <v>10.15230669433915</v>
       </c>
       <c r="N25" t="n">
-        <v>156.9788482699592</v>
+        <v>156.0417842762566</v>
       </c>
       <c r="O25" t="n">
-        <v>12.52912001179489</v>
+        <v>12.4916685945576</v>
       </c>
       <c r="P25" t="n">
-        <v>331.1503045090537</v>
+        <v>331.1899374209424</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -25345,28 +25463,28 @@
         <v>0.064</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2556234690388269</v>
+        <v>0.2485294085012517</v>
       </c>
       <c r="J26" t="n">
+        <v>194</v>
+      </c>
+      <c r="K26" t="n">
         <v>193</v>
       </c>
-      <c r="K26" t="n">
-        <v>192</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.02251226989572452</v>
+        <v>0.02154128199875427</v>
       </c>
       <c r="M26" t="n">
-        <v>11.16509524988806</v>
+        <v>11.10997681311021</v>
       </c>
       <c r="N26" t="n">
-        <v>191.618207278409</v>
+        <v>190.5373005764231</v>
       </c>
       <c r="O26" t="n">
-        <v>13.84262284678771</v>
+        <v>13.80352493301704</v>
       </c>
       <c r="P26" t="n">
-        <v>327.625071820676</v>
+        <v>327.691821743143</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -25423,28 +25541,28 @@
         <v>0.0554</v>
       </c>
       <c r="I27" t="n">
-        <v>0.361418435550555</v>
+        <v>0.3564040214311942</v>
       </c>
       <c r="J27" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K27" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L27" t="n">
-        <v>0.03710662263429176</v>
+        <v>0.03647094707666987</v>
       </c>
       <c r="M27" t="n">
-        <v>11.93473776027656</v>
+        <v>11.9129582482844</v>
       </c>
       <c r="N27" t="n">
-        <v>227.9678338257908</v>
+        <v>226.9508138734508</v>
       </c>
       <c r="O27" t="n">
-        <v>15.09860370450827</v>
+        <v>15.06488678594867</v>
       </c>
       <c r="P27" t="n">
-        <v>321.0555582831265</v>
+        <v>321.1031049256366</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -25501,28 +25619,28 @@
         <v>0.0452</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2457136141263087</v>
+        <v>0.2419473748238817</v>
       </c>
       <c r="J28" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K28" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02215095369794928</v>
+        <v>0.02170714825311448</v>
       </c>
       <c r="M28" t="n">
-        <v>10.84455329004882</v>
+        <v>10.81005339494056</v>
       </c>
       <c r="N28" t="n">
-        <v>179.2520058126731</v>
+        <v>178.4171987704448</v>
       </c>
       <c r="O28" t="n">
-        <v>13.38850274723328</v>
+        <v>13.35729009831129</v>
       </c>
       <c r="P28" t="n">
-        <v>323.1280378715778</v>
+        <v>323.1637493284812</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -25579,28 +25697,28 @@
         <v>0.0527</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1914136640896963</v>
+        <v>0.187111766361941</v>
       </c>
       <c r="J29" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K29" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01644334802406033</v>
+        <v>0.0158781044230647</v>
       </c>
       <c r="M29" t="n">
-        <v>10.22792214303767</v>
+        <v>10.19902776514119</v>
       </c>
       <c r="N29" t="n">
-        <v>147.3944740432058</v>
+        <v>146.7510502095915</v>
       </c>
       <c r="O29" t="n">
-        <v>12.14061258928914</v>
+        <v>12.11408478629696</v>
       </c>
       <c r="P29" t="n">
-        <v>322.6550250857354</v>
+        <v>322.6958156523913</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -25657,28 +25775,28 @@
         <v>0.0524</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2424217032732456</v>
+        <v>0.2380317792120711</v>
       </c>
       <c r="J30" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K30" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02455428660862835</v>
+        <v>0.02392460486960046</v>
       </c>
       <c r="M30" t="n">
-        <v>10.19788839006026</v>
+        <v>10.17043859821157</v>
       </c>
       <c r="N30" t="n">
-        <v>157.0163861087826</v>
+        <v>156.3281747109113</v>
       </c>
       <c r="O30" t="n">
-        <v>12.5306179460066</v>
+        <v>12.503126597412</v>
       </c>
       <c r="P30" t="n">
-        <v>321.4969089232951</v>
+        <v>321.5385341550798</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -25735,28 +25853,28 @@
         <v>0.0501</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3389885763806103</v>
+        <v>0.3324665743013526</v>
       </c>
       <c r="J31" t="n">
+        <v>194</v>
+      </c>
+      <c r="K31" t="n">
         <v>193</v>
       </c>
-      <c r="K31" t="n">
-        <v>192</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.05413973323732824</v>
+        <v>0.0526153135770715</v>
       </c>
       <c r="M31" t="n">
-        <v>9.108847781058934</v>
+        <v>9.102689778730793</v>
       </c>
       <c r="N31" t="n">
-        <v>135.1424181183098</v>
+        <v>134.7104416124595</v>
       </c>
       <c r="O31" t="n">
-        <v>11.62507712311234</v>
+        <v>11.60648274079876</v>
       </c>
       <c r="P31" t="n">
-        <v>319.2748901034209</v>
+        <v>319.3368302236936</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -25813,28 +25931,28 @@
         <v>0.0491</v>
       </c>
       <c r="I32" t="n">
-        <v>0.29735968675642</v>
+        <v>0.293122152628049</v>
       </c>
       <c r="J32" t="n">
+        <v>194</v>
+      </c>
+      <c r="K32" t="n">
         <v>193</v>
       </c>
-      <c r="K32" t="n">
-        <v>192</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.05574568532405699</v>
+        <v>0.05474575514773927</v>
       </c>
       <c r="M32" t="n">
-        <v>7.938529422024897</v>
+        <v>7.923321562281508</v>
       </c>
       <c r="N32" t="n">
-        <v>100.8213686917307</v>
+        <v>100.412216495358</v>
       </c>
       <c r="O32" t="n">
-        <v>10.04098444833626</v>
+        <v>10.02058962812858</v>
       </c>
       <c r="P32" t="n">
-        <v>316.7659197907683</v>
+        <v>316.8061640854468</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -25891,28 +26009,28 @@
         <v>0.0427</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2345230820122387</v>
+        <v>0.2259662094784048</v>
       </c>
       <c r="J33" t="n">
+        <v>194</v>
+      </c>
+      <c r="K33" t="n">
         <v>193</v>
       </c>
-      <c r="K33" t="n">
-        <v>192</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.03035117715462821</v>
+        <v>0.0284242601575857</v>
       </c>
       <c r="M33" t="n">
-        <v>8.522041902618939</v>
+        <v>8.521230835943806</v>
       </c>
       <c r="N33" t="n">
-        <v>118.2825855795232</v>
+        <v>118.1314620240428</v>
       </c>
       <c r="O33" t="n">
-        <v>10.87577976880385</v>
+        <v>10.86882983692554</v>
       </c>
       <c r="P33" t="n">
-        <v>315.3088968666972</v>
+        <v>315.3901623596338</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -25950,7 +26068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH194"/>
+  <dimension ref="A1:AH195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59055,17 +59173,17 @@
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>-34.4384271520361,173.00608692295222</t>
+          <t>-34.43841609814587,173.00602243520214</t>
         </is>
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>-34.43915035621329,173.00583312377248</t>
+          <t>-34.43914450143533,173.00578487390442</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>-34.43988752269746,173.00568334338593</t>
+          <t>-34.43988147571911,173.00562085256357</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -59106,6 +59224,178 @@
       <c r="AH194" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>-34.42297229239592,173.01238184614496</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>-34.42360605999221,173.0119128645261</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>-34.42424467629503,173.01145506527163</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-34.424948106525946,173.011146598128</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-34.42560964415532,173.01074162952696</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-34.426282098547794,173.01036182335778</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-34.42699170749431,173.01006762788109</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-34.427694574425544,173.00975791234916</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-34.42840075007906,173.00941954301626</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>-34.429097363057245,173.00905685836491</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>-34.42979539859682,173.00874417751288</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>-34.430499863373846,173.00846577789528</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>-34.43119628864852,173.00815756970343</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>-34.431926041766154,173.0079730469069</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>-34.43263592651007,173.00770850925338</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>-34.43335836010912,173.00747145519827</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>-34.43406924981856,173.00718298759895</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>-34.434779439341845,173.0069212433435</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>-34.435502071473955,173.00672271763415</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>-34.43621879611568,173.00649422349676</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>-34.43694800528864,173.00632916128993</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>-34.437675686068644,173.00615636926017</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>-34.43841200545723,173.00599855875024</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>-34.43914373038056,173.00577851956962</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>-34.439880408601965,173.00560982477234</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>-34.44060876384765,173.0054281244407</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>-34.441344948634985,173.0053274027494</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>-34.44207812429746,173.00519565114266</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>-34.44281406594595,173.00509255068462</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>-34.44355517096933,173.00496576181325</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>-34.4443025908028,173.00488208358323</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>-34.44503947066962,173.00473577632906</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
